--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/o-higgins.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -554,7 +554,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE TRANSPORTE JIMÉNEZ HERMANOS LTDA.</t>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE TRANSPORTE JIMÉNEZ HERMANOS LTDA.</t>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1180,6 +1180,189 @@
       </c>
       <c r="M12" s="2" t="n">
         <v>35882.19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1398-1092-CM26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.606.800-8</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ABRAHAM PATRICIO VILLANUEVA MICHEA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>15.751.336-2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>8873.370000000001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>615-72-CM26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>61.802.006-1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>VERÓNICA LOURDES SANDOVAL VALENZUELA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>12.690.978-0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>30937.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>973155-2-CM26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>60.803.435-8</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>76.036.979-9</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>618.75</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/o-higgins.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/o-higgins.xlsx
@@ -1233,7 +1233,11 @@
           <t>15.751.336-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/o-higgins.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1367,6 +1367,67 @@
       </c>
       <c r="M15" s="2" t="n">
         <v>618.75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>932-173-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>76.036.979-9</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>1859.18</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/o-higgins.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/o-higgins.xlsx
@@ -778,7 +778,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
